--- a/nr-split-menu-transactions/ig/StructureDefinition-Folder.xlsx
+++ b/nr-split-menu-transactions/ig/StructureDefinition-Folder.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:11:29+00:00</t>
+    <t>2026-06-17T14:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-split-menu-transactions/ig/StructureDefinition-Folder.xlsx
+++ b/nr-split-menu-transactions/ig/StructureDefinition-Folder.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:20:26+00:00</t>
+    <t>2026-06-17T14:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
